--- a/output/yearly_population_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_96_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>5218</v>
       </c>
       <c r="C2" t="n">
-        <v>7434</v>
+        <v>8662</v>
       </c>
       <c r="D2" t="n">
-        <v>35605</v>
+        <v>33430</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2731</v>
+        <v>2864</v>
       </c>
       <c r="C3" t="n">
-        <v>8291</v>
+        <v>5722</v>
       </c>
       <c r="D3" t="n">
-        <v>17654</v>
+        <v>18490</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2238</v>
+        <v>2457</v>
       </c>
       <c r="C4" t="n">
-        <v>7227</v>
+        <v>6063</v>
       </c>
       <c r="D4" t="n">
-        <v>8525</v>
+        <v>7566</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1506</v>
+        <v>1561</v>
       </c>
       <c r="C5" t="n">
-        <v>5241</v>
+        <v>5313</v>
       </c>
       <c r="D5" t="n">
-        <v>3405</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>806</v>
+        <v>857</v>
       </c>
       <c r="C6" t="n">
-        <v>3041</v>
+        <v>3919</v>
       </c>
       <c r="D6" t="n">
-        <v>1329</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="C7" t="n">
-        <v>1370</v>
+        <v>2356</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>561</v>
+        <v>1085</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4834</v>
+        <v>6652</v>
       </c>
       <c r="C2" t="n">
-        <v>13892</v>
+        <v>14242</v>
       </c>
       <c r="D2" t="n">
-        <v>27319</v>
+        <v>40368</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2758</v>
+        <v>3133</v>
       </c>
       <c r="C3" t="n">
-        <v>7032</v>
+        <v>6182</v>
       </c>
       <c r="D3" t="n">
-        <v>18908</v>
+        <v>19189</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2098</v>
+        <v>2253</v>
       </c>
       <c r="C4" t="n">
-        <v>7507</v>
+        <v>5779</v>
       </c>
       <c r="D4" t="n">
-        <v>9755</v>
+        <v>8941</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1611</v>
+        <v>1725</v>
       </c>
       <c r="C5" t="n">
-        <v>5996</v>
+        <v>5482</v>
       </c>
       <c r="D5" t="n">
-        <v>4055</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1011</v>
+        <v>1040</v>
       </c>
       <c r="C6" t="n">
-        <v>4003</v>
+        <v>4484</v>
       </c>
       <c r="D6" t="n">
-        <v>1630</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="C7" t="n">
-        <v>2092</v>
+        <v>2990</v>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C8" t="n">
-        <v>909</v>
+        <v>1597</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>696</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5290</v>
+        <v>6513</v>
       </c>
       <c r="C2" t="n">
-        <v>9623</v>
+        <v>12209</v>
       </c>
       <c r="D2" t="n">
-        <v>27076</v>
+        <v>36080</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2949</v>
+        <v>3624</v>
       </c>
       <c r="C3" t="n">
-        <v>8714</v>
+        <v>8282</v>
       </c>
       <c r="D3" t="n">
-        <v>18707</v>
+        <v>20502</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2013</v>
+        <v>2208</v>
       </c>
       <c r="C4" t="n">
-        <v>7073</v>
+        <v>5769</v>
       </c>
       <c r="D4" t="n">
-        <v>10682</v>
+        <v>10144</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1611</v>
+        <v>1723</v>
       </c>
       <c r="C5" t="n">
-        <v>6509</v>
+        <v>5487</v>
       </c>
       <c r="D5" t="n">
-        <v>4752</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1137</v>
+        <v>1195</v>
       </c>
       <c r="C6" t="n">
-        <v>4732</v>
+        <v>4785</v>
       </c>
       <c r="D6" t="n">
-        <v>1918</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="C7" t="n">
-        <v>2838</v>
+        <v>3530</v>
       </c>
       <c r="D7" t="n">
-        <v>878</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C8" t="n">
-        <v>1372</v>
+        <v>2099</v>
       </c>
       <c r="D8" t="n">
-        <v>498</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>1022</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>434</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4891</v>
+        <v>6080</v>
       </c>
       <c r="C2" t="n">
-        <v>6620</v>
+        <v>8595</v>
       </c>
       <c r="D2" t="n">
-        <v>22558</v>
+        <v>29848</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3574</v>
+        <v>4104</v>
       </c>
       <c r="C3" t="n">
-        <v>12362</v>
+        <v>11614</v>
       </c>
       <c r="D3" t="n">
-        <v>20342</v>
+        <v>21814</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1488</v>
+        <v>1592</v>
       </c>
       <c r="C4" t="n">
-        <v>10118</v>
+        <v>8313</v>
       </c>
       <c r="D4" t="n">
-        <v>10257</v>
+        <v>9299</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1050</v>
+        <v>1104</v>
       </c>
       <c r="C5" t="n">
-        <v>4637</v>
+        <v>4689</v>
       </c>
       <c r="D5" t="n">
-        <v>3156</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="C6" t="n">
-        <v>2781</v>
+        <v>3459</v>
       </c>
       <c r="D6" t="n">
-        <v>860</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>1344</v>
+        <v>2057</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>565</v>
+        <v>1001</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2999</v>
+        <v>3592</v>
       </c>
       <c r="C2" t="n">
-        <v>3569</v>
+        <v>3937</v>
       </c>
       <c r="D2" t="n">
-        <v>15539</v>
+        <v>20628</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3574</v>
+        <v>4274</v>
       </c>
       <c r="C3" t="n">
-        <v>8872</v>
+        <v>9389</v>
       </c>
       <c r="D3" t="n">
-        <v>19666</v>
+        <v>21620</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1986</v>
+        <v>2163</v>
       </c>
       <c r="C4" t="n">
-        <v>11330</v>
+        <v>9837</v>
       </c>
       <c r="D4" t="n">
-        <v>11495</v>
+        <v>10997</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1161</v>
+        <v>1209</v>
       </c>
       <c r="C5" t="n">
-        <v>6928</v>
+        <v>6242</v>
       </c>
       <c r="D5" t="n">
-        <v>4006</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>3592</v>
+        <v>4038</v>
       </c>
       <c r="D6" t="n">
-        <v>1095</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>1842</v>
+        <v>2594</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>769</v>
+        <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -2125,7 +2125,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>462</v>
       </c>
       <c r="D9" t="n">
         <v>257</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>165</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3507</v>
+        <v>3538</v>
       </c>
       <c r="C2" t="n">
-        <v>6930</v>
+        <v>14161</v>
       </c>
       <c r="D2" t="n">
-        <v>15827</v>
+        <v>17081</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2804</v>
+        <v>3363</v>
       </c>
       <c r="C3" t="n">
-        <v>5714</v>
+        <v>6171</v>
       </c>
       <c r="D3" t="n">
-        <v>17783</v>
+        <v>20239</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2297</v>
+        <v>2617</v>
       </c>
       <c r="C4" t="n">
-        <v>9914</v>
+        <v>9421</v>
       </c>
       <c r="D4" t="n">
-        <v>12479</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1340</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="n">
-        <v>8812</v>
+        <v>7794</v>
       </c>
       <c r="D5" t="n">
-        <v>5034</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="C6" t="n">
-        <v>5065</v>
+        <v>4931</v>
       </c>
       <c r="D6" t="n">
-        <v>1499</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C7" t="n">
-        <v>2578</v>
+        <v>3212</v>
       </c>
       <c r="D7" t="n">
-        <v>611</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>1207</v>
+        <v>1807</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>495</v>
+        <v>762</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
         <v>168</v>
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2079</v>
+        <v>2132</v>
       </c>
       <c r="C2" t="n">
-        <v>3306</v>
+        <v>6823</v>
       </c>
       <c r="D2" t="n">
-        <v>11038</v>
+        <v>11922</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2864</v>
+        <v>3285</v>
       </c>
       <c r="C3" t="n">
-        <v>5948</v>
+        <v>8559</v>
       </c>
       <c r="D3" t="n">
-        <v>17181</v>
+        <v>19457</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2527</v>
+        <v>2861</v>
       </c>
       <c r="C4" t="n">
-        <v>9328</v>
+        <v>9221</v>
       </c>
       <c r="D4" t="n">
-        <v>13205</v>
+        <v>13299</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1402</v>
+        <v>1466</v>
       </c>
       <c r="C5" t="n">
-        <v>10333</v>
+        <v>9362</v>
       </c>
       <c r="D5" t="n">
-        <v>5305</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="C6" t="n">
-        <v>5922</v>
+        <v>5771</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>2520</v>
+        <v>3303</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>839</v>
+        <v>1260</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
         <v>164</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1952</v>
+        <v>2802</v>
       </c>
       <c r="C2" t="n">
-        <v>5419</v>
+        <v>7945</v>
       </c>
       <c r="D2" t="n">
-        <v>12613</v>
+        <v>16605</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2178</v>
+        <v>2428</v>
       </c>
       <c r="C3" t="n">
-        <v>4265</v>
+        <v>6974</v>
       </c>
       <c r="D3" t="n">
-        <v>15267</v>
+        <v>17216</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2326</v>
+        <v>2644</v>
       </c>
       <c r="C4" t="n">
-        <v>7666</v>
+        <v>8819</v>
       </c>
       <c r="D4" t="n">
-        <v>13414</v>
+        <v>13840</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1647</v>
+        <v>1776</v>
       </c>
       <c r="C5" t="n">
-        <v>9783</v>
+        <v>9197</v>
       </c>
       <c r="D5" t="n">
-        <v>6281</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>867</v>
       </c>
       <c r="C6" t="n">
-        <v>7706</v>
+        <v>7191</v>
       </c>
       <c r="D6" t="n">
-        <v>1969</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>3843</v>
+        <v>4253</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1448</v>
+        <v>1984</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>438</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1290</v>
+        <v>1855</v>
       </c>
       <c r="C2" t="n">
-        <v>3756</v>
+        <v>4291</v>
       </c>
       <c r="D2" t="n">
-        <v>10089</v>
+        <v>12630</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1848</v>
+        <v>2229</v>
       </c>
       <c r="C3" t="n">
-        <v>4279</v>
+        <v>6753</v>
       </c>
       <c r="D3" t="n">
-        <v>14163</v>
+        <v>16238</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2103</v>
+        <v>2381</v>
       </c>
       <c r="C4" t="n">
-        <v>6388</v>
+        <v>8114</v>
       </c>
       <c r="D4" t="n">
-        <v>13366</v>
+        <v>13973</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>1911</v>
       </c>
       <c r="C5" t="n">
-        <v>9223</v>
+        <v>9231</v>
       </c>
       <c r="D5" t="n">
-        <v>6963</v>
+        <v>6469</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="n">
-        <v>8632</v>
+        <v>8057</v>
       </c>
       <c r="D6" t="n">
-        <v>2315</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>4938</v>
+        <v>5176</v>
       </c>
       <c r="D7" t="n">
-        <v>785</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1967</v>
+        <v>2488</v>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>491</v>
+        <v>638</v>
       </c>
       <c r="D9" t="n">
         <v>288</v>
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
         <v>36</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1861</v>
+        <v>2727</v>
       </c>
       <c r="C2" t="n">
-        <v>10434</v>
+        <v>15620</v>
       </c>
       <c r="D2" t="n">
-        <v>13182</v>
+        <v>20669</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1400</v>
+        <v>1776</v>
       </c>
       <c r="C3" t="n">
-        <v>3674</v>
+        <v>5266</v>
       </c>
       <c r="D3" t="n">
-        <v>12903</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1753</v>
+        <v>2026</v>
       </c>
       <c r="C4" t="n">
-        <v>5343</v>
+        <v>7409</v>
       </c>
       <c r="D4" t="n">
-        <v>12938</v>
+        <v>13852</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1708</v>
+        <v>1882</v>
       </c>
       <c r="C5" t="n">
-        <v>7915</v>
+        <v>8620</v>
       </c>
       <c r="D5" t="n">
-        <v>7611</v>
+        <v>7208</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1153</v>
+        <v>1197</v>
       </c>
       <c r="C6" t="n">
-        <v>8782</v>
+        <v>8411</v>
       </c>
       <c r="D6" t="n">
-        <v>2865</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C7" t="n">
-        <v>6323</v>
+        <v>6162</v>
       </c>
       <c r="D7" t="n">
-        <v>956</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>2956</v>
+        <v>3356</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>958</v>
+        <v>1206</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D12" t="n">
         <v>92</v>
-      </c>
-      <c r="D12" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3749</v>
+        <v>4510</v>
       </c>
       <c r="C2" t="n">
-        <v>2594</v>
+        <v>10614</v>
       </c>
       <c r="D2" t="n">
-        <v>15476</v>
+        <v>8954</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1359</v>
+        <v>2013</v>
       </c>
       <c r="C2" t="n">
-        <v>6093</v>
+        <v>9373</v>
       </c>
       <c r="D2" t="n">
-        <v>9807</v>
+        <v>15377</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1909</v>
+        <v>2378</v>
       </c>
       <c r="C3" t="n">
-        <v>5463</v>
+        <v>7967</v>
       </c>
       <c r="D3" t="n">
-        <v>14118</v>
+        <v>16448</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2473</v>
+        <v>2774</v>
       </c>
       <c r="C4" t="n">
-        <v>8030</v>
+        <v>10220</v>
       </c>
       <c r="D4" t="n">
-        <v>13253</v>
+        <v>14033</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1081</v>
+        <v>1106</v>
       </c>
       <c r="C5" t="n">
-        <v>12072</v>
+        <v>12220</v>
       </c>
       <c r="D5" t="n">
-        <v>6911</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C6" t="n">
-        <v>7745</v>
+        <v>7440</v>
       </c>
       <c r="D6" t="n">
-        <v>2190</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2896</v>
+        <v>3288</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>938</v>
+        <v>1181</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>83</v>
+      </c>
+      <c r="D11" t="n">
         <v>90</v>
-      </c>
-      <c r="D11" t="n">
-        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5231</v>
+        <v>5991</v>
       </c>
       <c r="C2" t="n">
-        <v>4960</v>
+        <v>6846</v>
       </c>
       <c r="D2" t="n">
-        <v>20608</v>
+        <v>15304</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1595</v>
+        <v>1917</v>
       </c>
       <c r="C3" t="n">
-        <v>1307</v>
+        <v>5349</v>
       </c>
       <c r="D3" t="n">
-        <v>3239</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3926</v>
+        <v>4665</v>
       </c>
       <c r="C2" t="n">
-        <v>5656</v>
+        <v>7929</v>
       </c>
       <c r="D2" t="n">
-        <v>33421</v>
+        <v>19656</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2800</v>
+        <v>3244</v>
       </c>
       <c r="C3" t="n">
-        <v>2936</v>
+        <v>5343</v>
       </c>
       <c r="D3" t="n">
-        <v>5918</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>726</v>
+        <v>867</v>
       </c>
       <c r="C4" t="n">
-        <v>821</v>
+        <v>3178</v>
       </c>
       <c r="D4" t="n">
-        <v>1834</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4248</v>
+        <v>4003</v>
       </c>
       <c r="C2" t="n">
-        <v>8465</v>
+        <v>10159</v>
       </c>
       <c r="D2" t="n">
-        <v>28172</v>
+        <v>18786</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2755</v>
+        <v>3238</v>
       </c>
       <c r="C3" t="n">
-        <v>3825</v>
+        <v>5845</v>
       </c>
       <c r="D3" t="n">
-        <v>9892</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1490</v>
+        <v>1745</v>
       </c>
       <c r="C4" t="n">
-        <v>2001</v>
+        <v>4338</v>
       </c>
       <c r="D4" t="n">
-        <v>2562</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>359</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>542</v>
+        <v>1833</v>
       </c>
       <c r="D5" t="n">
-        <v>1256</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4729</v>
+        <v>4863</v>
       </c>
       <c r="C2" t="n">
-        <v>11145</v>
+        <v>8905</v>
       </c>
       <c r="D2" t="n">
-        <v>22339</v>
+        <v>23910</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2841</v>
+        <v>2962</v>
       </c>
       <c r="C3" t="n">
-        <v>5439</v>
+        <v>7020</v>
       </c>
       <c r="D3" t="n">
-        <v>11974</v>
+        <v>7806</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1788</v>
+        <v>2086</v>
       </c>
       <c r="C4" t="n">
-        <v>2957</v>
+        <v>5057</v>
       </c>
       <c r="D4" t="n">
-        <v>3796</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>769</v>
+        <v>884</v>
       </c>
       <c r="C5" t="n">
-        <v>1301</v>
+        <v>3093</v>
       </c>
       <c r="D5" t="n">
-        <v>1456</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>421</v>
+        <v>1061</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5650</v>
+        <v>6293</v>
       </c>
       <c r="C2" t="n">
-        <v>9675</v>
+        <v>8116</v>
       </c>
       <c r="D2" t="n">
-        <v>31441</v>
+        <v>40842</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2746</v>
+        <v>2822</v>
       </c>
       <c r="C3" t="n">
-        <v>6885</v>
+        <v>6529</v>
       </c>
       <c r="D3" t="n">
-        <v>11955</v>
+        <v>9129</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1446</v>
+        <v>1568</v>
       </c>
       <c r="C4" t="n">
-        <v>3567</v>
+        <v>4969</v>
       </c>
       <c r="D4" t="n">
-        <v>4482</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>664</v>
+        <v>764</v>
       </c>
       <c r="C5" t="n">
-        <v>1593</v>
+        <v>3001</v>
       </c>
       <c r="D5" t="n">
-        <v>1490</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>579</v>
+        <v>1383</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>247</v>
+        <v>446</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3800</v>
+        <v>4401</v>
       </c>
       <c r="C2" t="n">
-        <v>11557</v>
+        <v>8537</v>
       </c>
       <c r="D2" t="n">
-        <v>28499</v>
+        <v>40778</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3495</v>
+        <v>3771</v>
       </c>
       <c r="C3" t="n">
-        <v>7333</v>
+        <v>6407</v>
       </c>
       <c r="D3" t="n">
-        <v>14485</v>
+        <v>13784</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1843</v>
+        <v>1918</v>
       </c>
       <c r="C4" t="n">
-        <v>5531</v>
+        <v>5794</v>
       </c>
       <c r="D4" t="n">
-        <v>5924</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>935</v>
+        <v>1027</v>
       </c>
       <c r="C5" t="n">
-        <v>2734</v>
+        <v>4043</v>
       </c>
       <c r="D5" t="n">
-        <v>2047</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="C6" t="n">
-        <v>1155</v>
+        <v>2282</v>
       </c>
       <c r="D6" t="n">
-        <v>902</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>435</v>
+        <v>969</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>235</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3671</v>
+        <v>3583</v>
       </c>
       <c r="C2" t="n">
-        <v>10666</v>
+        <v>6391</v>
       </c>
       <c r="D2" t="n">
-        <v>36859</v>
+        <v>35933</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3008</v>
+        <v>3360</v>
       </c>
       <c r="C3" t="n">
-        <v>8341</v>
+        <v>6537</v>
       </c>
       <c r="D3" t="n">
-        <v>15684</v>
+        <v>16916</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2275</v>
+        <v>2424</v>
       </c>
       <c r="C4" t="n">
-        <v>6436</v>
+        <v>5953</v>
       </c>
       <c r="D4" t="n">
-        <v>7387</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1220</v>
+        <v>1273</v>
       </c>
       <c r="C5" t="n">
-        <v>4181</v>
+        <v>4900</v>
       </c>
       <c r="D5" t="n">
-        <v>2672</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>610</v>
+        <v>677</v>
       </c>
       <c r="C6" t="n">
-        <v>1990</v>
+        <v>3169</v>
       </c>
       <c r="D6" t="n">
-        <v>1098</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>815</v>
+        <v>1637</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>645</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_96_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5218</v>
+        <v>8566</v>
       </c>
       <c r="C2" t="n">
-        <v>8662</v>
+        <v>10584</v>
       </c>
       <c r="D2" t="n">
-        <v>33430</v>
+        <v>22887</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2864</v>
+        <v>4817</v>
       </c>
       <c r="C3" t="n">
-        <v>5722</v>
+        <v>4629</v>
       </c>
       <c r="D3" t="n">
-        <v>18490</v>
+        <v>13254</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2457</v>
+        <v>3501</v>
       </c>
       <c r="C4" t="n">
-        <v>6063</v>
+        <v>5294</v>
       </c>
       <c r="D4" t="n">
-        <v>7566</v>
+        <v>7208</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1561</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>5313</v>
+        <v>5326</v>
       </c>
       <c r="D5" t="n">
-        <v>2542</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>857</v>
+        <v>1164</v>
       </c>
       <c r="C6" t="n">
-        <v>3919</v>
+        <v>3902</v>
       </c>
       <c r="D6" t="n">
-        <v>1107</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>406</v>
+        <v>594</v>
       </c>
       <c r="C7" t="n">
-        <v>2356</v>
+        <v>2192</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>1085</v>
+        <v>978</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>436</v>
+        <v>399</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>163</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6652</v>
+        <v>9638</v>
       </c>
       <c r="C2" t="n">
-        <v>14242</v>
+        <v>8218</v>
       </c>
       <c r="D2" t="n">
-        <v>40368</v>
+        <v>24241</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3133</v>
+        <v>5203</v>
       </c>
       <c r="C3" t="n">
-        <v>6182</v>
+        <v>6375</v>
       </c>
       <c r="D3" t="n">
-        <v>19189</v>
+        <v>13617</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2253</v>
+        <v>3461</v>
       </c>
       <c r="C4" t="n">
-        <v>5779</v>
+        <v>4877</v>
       </c>
       <c r="D4" t="n">
-        <v>8941</v>
+        <v>7848</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1725</v>
+        <v>2341</v>
       </c>
       <c r="C5" t="n">
-        <v>5482</v>
+        <v>5149</v>
       </c>
       <c r="D5" t="n">
-        <v>3236</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>1380</v>
       </c>
       <c r="C6" t="n">
-        <v>4484</v>
+        <v>4442</v>
       </c>
       <c r="D6" t="n">
-        <v>1288</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>528</v>
+        <v>743</v>
       </c>
       <c r="C7" t="n">
-        <v>2990</v>
+        <v>2928</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>326</v>
       </c>
       <c r="C8" t="n">
-        <v>1597</v>
+        <v>1467</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>696</v>
+        <v>631</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6513</v>
+        <v>9732</v>
       </c>
       <c r="C2" t="n">
-        <v>12209</v>
+        <v>9482</v>
       </c>
       <c r="D2" t="n">
-        <v>36080</v>
+        <v>22292</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3624</v>
+        <v>5612</v>
       </c>
       <c r="C3" t="n">
-        <v>8282</v>
+        <v>6381</v>
       </c>
       <c r="D3" t="n">
-        <v>20502</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2208</v>
+        <v>3512</v>
       </c>
       <c r="C4" t="n">
-        <v>5769</v>
+        <v>5347</v>
       </c>
       <c r="D4" t="n">
-        <v>10144</v>
+        <v>8440</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1723</v>
+        <v>2459</v>
       </c>
       <c r="C5" t="n">
-        <v>5487</v>
+        <v>4882</v>
       </c>
       <c r="D5" t="n">
-        <v>3873</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1195</v>
+        <v>1589</v>
       </c>
       <c r="C6" t="n">
-        <v>4785</v>
+        <v>4638</v>
       </c>
       <c r="D6" t="n">
-        <v>1533</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>644</v>
+        <v>887</v>
       </c>
       <c r="C7" t="n">
-        <v>3530</v>
+        <v>3520</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>430</v>
       </c>
       <c r="C8" t="n">
-        <v>2099</v>
+        <v>1996</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>1022</v>
+        <v>927</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
         <v>208</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -1556,7 +1556,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6080</v>
+        <v>9087</v>
       </c>
       <c r="C2" t="n">
-        <v>8595</v>
+        <v>6599</v>
       </c>
       <c r="D2" t="n">
-        <v>29848</v>
+        <v>18506</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4104</v>
+        <v>6482</v>
       </c>
       <c r="C3" t="n">
-        <v>11614</v>
+        <v>9370</v>
       </c>
       <c r="D3" t="n">
-        <v>21814</v>
+        <v>15379</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1592</v>
+        <v>2272</v>
       </c>
       <c r="C4" t="n">
-        <v>8313</v>
+        <v>7561</v>
       </c>
       <c r="D4" t="n">
-        <v>9299</v>
+        <v>8107</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1104</v>
+        <v>1468</v>
       </c>
       <c r="C5" t="n">
-        <v>4689</v>
+        <v>4545</v>
       </c>
       <c r="D5" t="n">
-        <v>2543</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>595</v>
+        <v>819</v>
       </c>
       <c r="C6" t="n">
-        <v>3459</v>
+        <v>3449</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>397</v>
       </c>
       <c r="C7" t="n">
-        <v>2057</v>
+        <v>1956</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>1001</v>
+        <v>908</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>203</v>
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>158</v>
@@ -1853,7 +1853,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>111</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3592</v>
+        <v>5493</v>
       </c>
       <c r="C2" t="n">
-        <v>3937</v>
+        <v>4098</v>
       </c>
       <c r="D2" t="n">
-        <v>20628</v>
+        <v>13208</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4274</v>
+        <v>6535</v>
       </c>
       <c r="C3" t="n">
-        <v>9389</v>
+        <v>7407</v>
       </c>
       <c r="D3" t="n">
-        <v>21620</v>
+        <v>15066</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2163</v>
+        <v>3293</v>
       </c>
       <c r="C4" t="n">
-        <v>9837</v>
+        <v>8437</v>
       </c>
       <c r="D4" t="n">
-        <v>10997</v>
+        <v>8985</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1209</v>
+        <v>1658</v>
       </c>
       <c r="C5" t="n">
-        <v>6242</v>
+        <v>5884</v>
       </c>
       <c r="D5" t="n">
-        <v>3292</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>704</v>
+        <v>963</v>
       </c>
       <c r="C6" t="n">
-        <v>4038</v>
+        <v>4028</v>
       </c>
       <c r="D6" t="n">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>2594</v>
+        <v>2488</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>1301</v>
+        <v>1209</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>162</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3538</v>
+        <v>5122</v>
       </c>
       <c r="C2" t="n">
-        <v>14161</v>
+        <v>8830</v>
       </c>
       <c r="D2" t="n">
-        <v>17081</v>
+        <v>13383</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3363</v>
+        <v>5130</v>
       </c>
       <c r="C3" t="n">
-        <v>6171</v>
+        <v>5227</v>
       </c>
       <c r="D3" t="n">
-        <v>20239</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2617</v>
+        <v>4022</v>
       </c>
       <c r="C4" t="n">
-        <v>9421</v>
+        <v>7767</v>
       </c>
       <c r="D4" t="n">
-        <v>12188</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>2061</v>
       </c>
       <c r="C5" t="n">
-        <v>7794</v>
+        <v>6938</v>
       </c>
       <c r="D5" t="n">
-        <v>4375</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>828</v>
+        <v>1141</v>
       </c>
       <c r="C6" t="n">
-        <v>4931</v>
+        <v>4848</v>
       </c>
       <c r="D6" t="n">
-        <v>1244</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>372</v>
+        <v>531</v>
       </c>
       <c r="C7" t="n">
-        <v>3212</v>
+        <v>3160</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>1807</v>
+        <v>1721</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>762</v>
+        <v>718</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
         <v>168</v>
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2132</v>
+        <v>3101</v>
       </c>
       <c r="C2" t="n">
-        <v>6823</v>
+        <v>4207</v>
       </c>
       <c r="D2" t="n">
-        <v>11922</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3285</v>
+        <v>4949</v>
       </c>
       <c r="C3" t="n">
-        <v>8559</v>
+        <v>6258</v>
       </c>
       <c r="D3" t="n">
-        <v>19457</v>
+        <v>13447</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>4394</v>
       </c>
       <c r="C4" t="n">
-        <v>9221</v>
+        <v>7546</v>
       </c>
       <c r="D4" t="n">
-        <v>13299</v>
+        <v>10267</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1466</v>
+        <v>2105</v>
       </c>
       <c r="C5" t="n">
-        <v>9362</v>
+        <v>8292</v>
       </c>
       <c r="D5" t="n">
-        <v>4496</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>665</v>
+        <v>943</v>
       </c>
       <c r="C6" t="n">
-        <v>5771</v>
+        <v>5706</v>
       </c>
       <c r="D6" t="n">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>3303</v>
+        <v>3255</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1260</v>
+        <v>1209</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
         <v>164</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2802</v>
+        <v>4389</v>
       </c>
       <c r="C2" t="n">
-        <v>7945</v>
+        <v>5771</v>
       </c>
       <c r="D2" t="n">
-        <v>16605</v>
+        <v>14347</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2428</v>
+        <v>3564</v>
       </c>
       <c r="C3" t="n">
-        <v>6974</v>
+        <v>4773</v>
       </c>
       <c r="D3" t="n">
-        <v>17216</v>
+        <v>12114</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2644</v>
+        <v>4077</v>
       </c>
       <c r="C4" t="n">
-        <v>8819</v>
+        <v>6795</v>
       </c>
       <c r="D4" t="n">
-        <v>13840</v>
+        <v>10443</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1776</v>
+        <v>2652</v>
       </c>
       <c r="C5" t="n">
-        <v>9197</v>
+        <v>7869</v>
       </c>
       <c r="D5" t="n">
-        <v>5670</v>
+        <v>4966</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>867</v>
+        <v>1247</v>
       </c>
       <c r="C6" t="n">
-        <v>7191</v>
+        <v>6778</v>
       </c>
       <c r="D6" t="n">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>4253</v>
+        <v>4278</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1984</v>
+        <v>1954</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1855</v>
+        <v>3120</v>
       </c>
       <c r="C2" t="n">
-        <v>4291</v>
+        <v>3196</v>
       </c>
       <c r="D2" t="n">
-        <v>12630</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2229</v>
+        <v>3349</v>
       </c>
       <c r="C3" t="n">
-        <v>6753</v>
+        <v>4734</v>
       </c>
       <c r="D3" t="n">
-        <v>16238</v>
+        <v>11839</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2381</v>
+        <v>3590</v>
       </c>
       <c r="C4" t="n">
-        <v>8114</v>
+        <v>5988</v>
       </c>
       <c r="D4" t="n">
-        <v>13973</v>
+        <v>10434</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1911</v>
+        <v>2920</v>
       </c>
       <c r="C5" t="n">
-        <v>9231</v>
+        <v>7626</v>
       </c>
       <c r="D5" t="n">
-        <v>6469</v>
+        <v>5441</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>1475</v>
       </c>
       <c r="C6" t="n">
-        <v>8057</v>
+        <v>7390</v>
       </c>
       <c r="D6" t="n">
-        <v>1928</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>5176</v>
+        <v>5157</v>
       </c>
       <c r="D7" t="n">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2488</v>
+        <v>2496</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>672</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2727</v>
+        <v>4604</v>
       </c>
       <c r="C2" t="n">
-        <v>15620</v>
+        <v>13067</v>
       </c>
       <c r="D2" t="n">
-        <v>20669</v>
+        <v>13742</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1776</v>
+        <v>2753</v>
       </c>
       <c r="C3" t="n">
-        <v>5266</v>
+        <v>3715</v>
       </c>
       <c r="D3" t="n">
-        <v>14820</v>
+        <v>10925</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2026</v>
+        <v>3047</v>
       </c>
       <c r="C4" t="n">
-        <v>7409</v>
+        <v>5345</v>
       </c>
       <c r="D4" t="n">
-        <v>13852</v>
+        <v>10319</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1882</v>
+        <v>2898</v>
       </c>
       <c r="C5" t="n">
-        <v>8620</v>
+        <v>6822</v>
       </c>
       <c r="D5" t="n">
-        <v>7208</v>
+        <v>5946</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1197</v>
+        <v>1790</v>
       </c>
       <c r="C6" t="n">
-        <v>8411</v>
+        <v>7417</v>
       </c>
       <c r="D6" t="n">
-        <v>2407</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>393</v>
+        <v>601</v>
       </c>
       <c r="C7" t="n">
-        <v>6162</v>
+        <v>5964</v>
       </c>
       <c r="D7" t="n">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>3356</v>
+        <v>3432</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1206</v>
+        <v>1243</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4510</v>
+        <v>9027</v>
       </c>
       <c r="C2" t="n">
-        <v>10614</v>
+        <v>8744</v>
       </c>
       <c r="D2" t="n">
-        <v>8954</v>
+        <v>5527</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2013</v>
+        <v>3331</v>
       </c>
       <c r="C2" t="n">
-        <v>9373</v>
+        <v>7631</v>
       </c>
       <c r="D2" t="n">
-        <v>15377</v>
+        <v>10225</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2378</v>
+        <v>3700</v>
       </c>
       <c r="C3" t="n">
-        <v>7967</v>
+        <v>6032</v>
       </c>
       <c r="D3" t="n">
-        <v>16448</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2774</v>
+        <v>4233</v>
       </c>
       <c r="C4" t="n">
-        <v>10220</v>
+        <v>7649</v>
       </c>
       <c r="D4" t="n">
-        <v>14033</v>
+        <v>10639</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1106</v>
+        <v>1707</v>
       </c>
       <c r="C5" t="n">
-        <v>12220</v>
+        <v>10275</v>
       </c>
       <c r="D5" t="n">
-        <v>6323</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>363</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>7440</v>
+        <v>7225</v>
       </c>
       <c r="D6" t="n">
-        <v>1888</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>3288</v>
+        <v>3363</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1181</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5991</v>
+        <v>8011</v>
       </c>
       <c r="C2" t="n">
-        <v>6846</v>
+        <v>7935</v>
       </c>
       <c r="D2" t="n">
-        <v>15304</v>
+        <v>18593</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1917</v>
+        <v>3833</v>
       </c>
       <c r="C3" t="n">
-        <v>5349</v>
+        <v>4406</v>
       </c>
       <c r="D3" t="n">
-        <v>2143</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,7 +4568,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4665</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="n">
-        <v>7929</v>
+        <v>7026</v>
       </c>
       <c r="D2" t="n">
-        <v>19656</v>
+        <v>16235</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3244</v>
+        <v>4868</v>
       </c>
       <c r="C3" t="n">
-        <v>5343</v>
+        <v>5521</v>
       </c>
       <c r="D3" t="n">
-        <v>4196</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>867</v>
+        <v>1699</v>
       </c>
       <c r="C4" t="n">
-        <v>3178</v>
+        <v>2626</v>
       </c>
       <c r="D4" t="n">
-        <v>1613</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4003</v>
+        <v>4942</v>
       </c>
       <c r="C2" t="n">
-        <v>10159</v>
+        <v>10242</v>
       </c>
       <c r="D2" t="n">
-        <v>18786</v>
+        <v>32506</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3238</v>
+        <v>4150</v>
       </c>
       <c r="C3" t="n">
-        <v>5845</v>
+        <v>5486</v>
       </c>
       <c r="D3" t="n">
-        <v>6367</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1745</v>
+        <v>2799</v>
       </c>
       <c r="C4" t="n">
-        <v>4338</v>
+        <v>4158</v>
       </c>
       <c r="D4" t="n">
-        <v>2059</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>742</v>
       </c>
       <c r="C5" t="n">
-        <v>1833</v>
+        <v>1533</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>174</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>76</v>
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4863</v>
+        <v>5620</v>
       </c>
       <c r="C2" t="n">
-        <v>8905</v>
+        <v>10871</v>
       </c>
       <c r="D2" t="n">
-        <v>23910</v>
+        <v>26517</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2962</v>
+        <v>3727</v>
       </c>
       <c r="C3" t="n">
-        <v>7020</v>
+        <v>6876</v>
       </c>
       <c r="D3" t="n">
-        <v>7806</v>
+        <v>9535</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2086</v>
+        <v>2961</v>
       </c>
       <c r="C4" t="n">
-        <v>5057</v>
+        <v>4772</v>
       </c>
       <c r="D4" t="n">
-        <v>2782</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>884</v>
+        <v>1440</v>
       </c>
       <c r="C5" t="n">
-        <v>3093</v>
+        <v>2821</v>
       </c>
       <c r="D5" t="n">
-        <v>1320</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>1061</v>
+        <v>914</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6293</v>
+        <v>8771</v>
       </c>
       <c r="C2" t="n">
-        <v>8116</v>
+        <v>6502</v>
       </c>
       <c r="D2" t="n">
-        <v>40842</v>
+        <v>30088</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2822</v>
+        <v>3360</v>
       </c>
       <c r="C3" t="n">
-        <v>6529</v>
+        <v>7278</v>
       </c>
       <c r="D3" t="n">
-        <v>9129</v>
+        <v>10767</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1568</v>
+        <v>2056</v>
       </c>
       <c r="C4" t="n">
-        <v>4969</v>
+        <v>4836</v>
       </c>
       <c r="D4" t="n">
-        <v>3152</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>764</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="n">
-        <v>3001</v>
+        <v>2763</v>
       </c>
       <c r="D5" t="n">
-        <v>1231</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>1383</v>
+        <v>1250</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>446</v>
+        <v>394</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4401</v>
+        <v>7751</v>
       </c>
       <c r="C2" t="n">
-        <v>8537</v>
+        <v>5673</v>
       </c>
       <c r="D2" t="n">
-        <v>40778</v>
+        <v>22090</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3771</v>
+        <v>5022</v>
       </c>
       <c r="C3" t="n">
-        <v>6407</v>
+        <v>5880</v>
       </c>
       <c r="D3" t="n">
-        <v>13784</v>
+        <v>13220</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1918</v>
+        <v>2364</v>
       </c>
       <c r="C4" t="n">
-        <v>5794</v>
+        <v>6188</v>
       </c>
       <c r="D4" t="n">
-        <v>4261</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1027</v>
+        <v>1429</v>
       </c>
       <c r="C5" t="n">
-        <v>4043</v>
+        <v>3899</v>
       </c>
       <c r="D5" t="n">
-        <v>1550</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>475</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>2282</v>
+        <v>2077</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>969</v>
+        <v>859</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>131</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3583</v>
+        <v>6636</v>
       </c>
       <c r="C2" t="n">
-        <v>6391</v>
+        <v>5584</v>
       </c>
       <c r="D2" t="n">
-        <v>35933</v>
+        <v>17494</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3360</v>
+        <v>5201</v>
       </c>
       <c r="C3" t="n">
-        <v>6537</v>
+        <v>5014</v>
       </c>
       <c r="D3" t="n">
-        <v>16916</v>
+        <v>13637</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2424</v>
+        <v>3141</v>
       </c>
       <c r="C4" t="n">
-        <v>5953</v>
+        <v>5831</v>
       </c>
       <c r="D4" t="n">
-        <v>5827</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1273</v>
+        <v>1652</v>
       </c>
       <c r="C5" t="n">
-        <v>4900</v>
+        <v>5048</v>
       </c>
       <c r="D5" t="n">
-        <v>1997</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>677</v>
+        <v>971</v>
       </c>
       <c r="C6" t="n">
-        <v>3169</v>
+        <v>2998</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>411</v>
       </c>
       <c r="C7" t="n">
-        <v>1637</v>
+        <v>1479</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>645</v>
+        <v>578</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6566,7 +6566,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_96_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8566</v>
+        <v>1094</v>
       </c>
       <c r="C2" t="n">
-        <v>10584</v>
+        <v>2653</v>
       </c>
       <c r="D2" t="n">
-        <v>22887</v>
+        <v>14898</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4817</v>
+        <v>1887</v>
       </c>
       <c r="C3" t="n">
-        <v>4629</v>
+        <v>5949</v>
       </c>
       <c r="D3" t="n">
-        <v>13254</v>
+        <v>15289</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3501</v>
+        <v>1449</v>
       </c>
       <c r="C4" t="n">
-        <v>5294</v>
+        <v>7939</v>
       </c>
       <c r="D4" t="n">
-        <v>7208</v>
+        <v>7537</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>845</v>
       </c>
       <c r="C5" t="n">
-        <v>5326</v>
+        <v>4618</v>
       </c>
       <c r="D5" t="n">
-        <v>2657</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1164</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>3902</v>
+        <v>1620</v>
       </c>
       <c r="D6" t="n">
-        <v>1113</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>594</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>2192</v>
+        <v>535</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>978</v>
+        <v>326</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9638</v>
+        <v>1070</v>
       </c>
       <c r="C2" t="n">
-        <v>8218</v>
+        <v>5622</v>
       </c>
       <c r="D2" t="n">
-        <v>24241</v>
+        <v>14233</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5203</v>
+        <v>1279</v>
       </c>
       <c r="C3" t="n">
-        <v>6375</v>
+        <v>3665</v>
       </c>
       <c r="D3" t="n">
-        <v>13617</v>
+        <v>14153</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3461</v>
+        <v>1443</v>
       </c>
       <c r="C4" t="n">
-        <v>4877</v>
+        <v>6761</v>
       </c>
       <c r="D4" t="n">
-        <v>7848</v>
+        <v>8721</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2341</v>
+        <v>999</v>
       </c>
       <c r="C5" t="n">
-        <v>5149</v>
+        <v>6243</v>
       </c>
       <c r="D5" t="n">
-        <v>3275</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1380</v>
+        <v>518</v>
       </c>
       <c r="C6" t="n">
-        <v>4442</v>
+        <v>3114</v>
       </c>
       <c r="D6" t="n">
-        <v>1309</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>743</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>2928</v>
+        <v>1061</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1467</v>
+        <v>426</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>631</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9732</v>
+        <v>570</v>
       </c>
       <c r="C2" t="n">
-        <v>9482</v>
+        <v>2352</v>
       </c>
       <c r="D2" t="n">
-        <v>22292</v>
+        <v>9595</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5612</v>
+        <v>1173</v>
       </c>
       <c r="C3" t="n">
-        <v>6381</v>
+        <v>4279</v>
       </c>
       <c r="D3" t="n">
-        <v>14020</v>
+        <v>13778</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3512</v>
+        <v>1574</v>
       </c>
       <c r="C4" t="n">
-        <v>5347</v>
+        <v>6115</v>
       </c>
       <c r="D4" t="n">
-        <v>8440</v>
+        <v>9583</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2459</v>
+        <v>1028</v>
       </c>
       <c r="C5" t="n">
-        <v>4882</v>
+        <v>7151</v>
       </c>
       <c r="D5" t="n">
-        <v>3758</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1589</v>
+        <v>403</v>
       </c>
       <c r="C6" t="n">
-        <v>4638</v>
+        <v>3991</v>
       </c>
       <c r="D6" t="n">
-        <v>1556</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>887</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3520</v>
+        <v>1026</v>
       </c>
       <c r="D7" t="n">
-        <v>767</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>430</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1996</v>
+        <v>447</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>927</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>405</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9087</v>
+        <v>1079</v>
       </c>
       <c r="C2" t="n">
-        <v>6599</v>
+        <v>7411</v>
       </c>
       <c r="D2" t="n">
-        <v>18506</v>
+        <v>11130</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6482</v>
+        <v>769</v>
       </c>
       <c r="C3" t="n">
-        <v>9370</v>
+        <v>2902</v>
       </c>
       <c r="D3" t="n">
-        <v>15379</v>
+        <v>12304</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2272</v>
+        <v>1244</v>
       </c>
       <c r="C4" t="n">
-        <v>7561</v>
+        <v>5077</v>
       </c>
       <c r="D4" t="n">
-        <v>8107</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1468</v>
+        <v>1144</v>
       </c>
       <c r="C5" t="n">
-        <v>4545</v>
+        <v>6553</v>
       </c>
       <c r="D5" t="n">
-        <v>2535</v>
+        <v>4411</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>598</v>
       </c>
       <c r="C6" t="n">
-        <v>3449</v>
+        <v>5514</v>
       </c>
       <c r="D6" t="n">
-        <v>751</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>1956</v>
+        <v>2353</v>
       </c>
       <c r="D7" t="n">
-        <v>461</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>908</v>
+        <v>688</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>50</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>4098</v>
+        <v>4080</v>
       </c>
       <c r="D2" t="n">
-        <v>13208</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6535</v>
+        <v>771</v>
       </c>
       <c r="C3" t="n">
-        <v>7407</v>
+        <v>4472</v>
       </c>
       <c r="D3" t="n">
-        <v>15066</v>
+        <v>11435</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3293</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="n">
-        <v>8437</v>
+        <v>4066</v>
       </c>
       <c r="D4" t="n">
-        <v>8985</v>
+        <v>10159</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1658</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="n">
-        <v>5884</v>
+        <v>6107</v>
       </c>
       <c r="D5" t="n">
-        <v>3226</v>
+        <v>5114</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>963</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>4028</v>
+        <v>6110</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>185</v>
       </c>
       <c r="C7" t="n">
-        <v>2488</v>
+        <v>3442</v>
       </c>
       <c r="D7" t="n">
-        <v>501</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1209</v>
+        <v>1097</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5122</v>
+        <v>724</v>
       </c>
       <c r="C2" t="n">
-        <v>8830</v>
+        <v>11567</v>
       </c>
       <c r="D2" t="n">
-        <v>13383</v>
+        <v>9076</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5130</v>
+        <v>591</v>
       </c>
       <c r="C3" t="n">
-        <v>5227</v>
+        <v>3811</v>
       </c>
       <c r="D3" t="n">
-        <v>13800</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4022</v>
+        <v>790</v>
       </c>
       <c r="C4" t="n">
-        <v>7767</v>
+        <v>4176</v>
       </c>
       <c r="D4" t="n">
-        <v>9704</v>
+        <v>10058</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2061</v>
+        <v>1014</v>
       </c>
       <c r="C5" t="n">
-        <v>6938</v>
+        <v>5039</v>
       </c>
       <c r="D5" t="n">
-        <v>4012</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1141</v>
+        <v>829</v>
       </c>
       <c r="C6" t="n">
-        <v>4848</v>
+        <v>6109</v>
       </c>
       <c r="D6" t="n">
-        <v>1238</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>3160</v>
+        <v>4564</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>821</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1721</v>
+        <v>2049</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>718</v>
+        <v>670</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3101</v>
+        <v>486</v>
       </c>
       <c r="C2" t="n">
-        <v>4207</v>
+        <v>6014</v>
       </c>
       <c r="D2" t="n">
-        <v>9345</v>
+        <v>6534</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4949</v>
+        <v>818</v>
       </c>
       <c r="C3" t="n">
-        <v>6258</v>
+        <v>6275</v>
       </c>
       <c r="D3" t="n">
-        <v>13447</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4394</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="n">
-        <v>7546</v>
+        <v>5937</v>
       </c>
       <c r="D4" t="n">
-        <v>10267</v>
+        <v>10438</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2105</v>
+        <v>840</v>
       </c>
       <c r="C5" t="n">
-        <v>8292</v>
+        <v>8021</v>
       </c>
       <c r="D5" t="n">
-        <v>4225</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>943</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>5706</v>
+        <v>5969</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>3255</v>
+        <v>2008</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1209</v>
+        <v>656</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4389</v>
+        <v>256</v>
       </c>
       <c r="C2" t="n">
-        <v>5771</v>
+        <v>2716</v>
       </c>
       <c r="D2" t="n">
-        <v>14347</v>
+        <v>5538</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3564</v>
+        <v>572</v>
       </c>
       <c r="C3" t="n">
-        <v>4773</v>
+        <v>5413</v>
       </c>
       <c r="D3" t="n">
-        <v>12114</v>
+        <v>9569</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4077</v>
+        <v>901</v>
       </c>
       <c r="C4" t="n">
-        <v>6795</v>
+        <v>5799</v>
       </c>
       <c r="D4" t="n">
-        <v>10443</v>
+        <v>9805</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2652</v>
+        <v>753</v>
       </c>
       <c r="C5" t="n">
-        <v>7869</v>
+        <v>6184</v>
       </c>
       <c r="D5" t="n">
-        <v>4966</v>
+        <v>5417</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1247</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>6778</v>
+        <v>5693</v>
       </c>
       <c r="D6" t="n">
-        <v>1603</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>4278</v>
+        <v>2661</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1954</v>
+        <v>768</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3120</v>
+        <v>495</v>
       </c>
       <c r="C2" t="n">
-        <v>3196</v>
+        <v>4372</v>
       </c>
       <c r="D2" t="n">
-        <v>10537</v>
+        <v>9920</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>353</v>
       </c>
       <c r="C3" t="n">
-        <v>4734</v>
+        <v>3464</v>
       </c>
       <c r="D3" t="n">
-        <v>11839</v>
+        <v>8235</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3590</v>
+        <v>656</v>
       </c>
       <c r="C4" t="n">
-        <v>5988</v>
+        <v>5463</v>
       </c>
       <c r="D4" t="n">
-        <v>10434</v>
+        <v>9461</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2920</v>
+        <v>748</v>
       </c>
       <c r="C5" t="n">
-        <v>7626</v>
+        <v>5907</v>
       </c>
       <c r="D5" t="n">
-        <v>5441</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1475</v>
+        <v>465</v>
       </c>
       <c r="C6" t="n">
-        <v>7390</v>
+        <v>5880</v>
       </c>
       <c r="D6" t="n">
-        <v>1921</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>5157</v>
+        <v>4201</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>2496</v>
+        <v>1665</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>488</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4604</v>
+        <v>570</v>
       </c>
       <c r="C2" t="n">
-        <v>13067</v>
+        <v>7209</v>
       </c>
       <c r="D2" t="n">
-        <v>13742</v>
+        <v>16877</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2753</v>
+        <v>342</v>
       </c>
       <c r="C3" t="n">
-        <v>3715</v>
+        <v>3416</v>
       </c>
       <c r="D3" t="n">
-        <v>10925</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3047</v>
+        <v>456</v>
       </c>
       <c r="C4" t="n">
-        <v>5345</v>
+        <v>4332</v>
       </c>
       <c r="D4" t="n">
-        <v>10319</v>
+        <v>8961</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2898</v>
+        <v>642</v>
       </c>
       <c r="C5" t="n">
-        <v>6822</v>
+        <v>5510</v>
       </c>
       <c r="D5" t="n">
-        <v>5946</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1790</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>7417</v>
+        <v>5831</v>
       </c>
       <c r="D6" t="n">
-        <v>2335</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>5964</v>
+        <v>4989</v>
       </c>
       <c r="D7" t="n">
-        <v>845</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>3432</v>
+        <v>2807</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1243</v>
+        <v>995</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9027</v>
+        <v>6040</v>
       </c>
       <c r="C2" t="n">
-        <v>8744</v>
+        <v>3651</v>
       </c>
       <c r="D2" t="n">
-        <v>5527</v>
+        <v>18145</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3331</v>
+        <v>707</v>
       </c>
       <c r="C2" t="n">
-        <v>7631</v>
+        <v>7389</v>
       </c>
       <c r="D2" t="n">
-        <v>10225</v>
+        <v>27227</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3700</v>
+        <v>357</v>
       </c>
       <c r="C3" t="n">
-        <v>6032</v>
+        <v>4473</v>
       </c>
       <c r="D3" t="n">
-        <v>11950</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4233</v>
+        <v>353</v>
       </c>
       <c r="C4" t="n">
-        <v>7649</v>
+        <v>3778</v>
       </c>
       <c r="D4" t="n">
-        <v>10639</v>
+        <v>8441</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1707</v>
+        <v>525</v>
       </c>
       <c r="C5" t="n">
-        <v>10275</v>
+        <v>4863</v>
       </c>
       <c r="D5" t="n">
-        <v>5425</v>
+        <v>6571</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="C6" t="n">
-        <v>7225</v>
+        <v>5637</v>
       </c>
       <c r="D6" t="n">
-        <v>1864</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>3363</v>
+        <v>5292</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>3703</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>1695</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>571</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8011</v>
+        <v>5846</v>
       </c>
       <c r="C2" t="n">
-        <v>7935</v>
+        <v>13103</v>
       </c>
       <c r="D2" t="n">
-        <v>18593</v>
+        <v>28428</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3833</v>
+        <v>1994</v>
       </c>
       <c r="C3" t="n">
-        <v>4406</v>
+        <v>1441</v>
       </c>
       <c r="D3" t="n">
-        <v>1567</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>3281</v>
       </c>
       <c r="C2" t="n">
-        <v>7026</v>
+        <v>4735</v>
       </c>
       <c r="D2" t="n">
-        <v>16235</v>
+        <v>28620</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4868</v>
+        <v>3306</v>
       </c>
       <c r="C3" t="n">
-        <v>5521</v>
+        <v>7311</v>
       </c>
       <c r="D3" t="n">
-        <v>4312</v>
+        <v>7311</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1699</v>
+        <v>946</v>
       </c>
       <c r="C4" t="n">
-        <v>2626</v>
+        <v>934</v>
       </c>
       <c r="D4" t="n">
-        <v>1497</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4942</v>
+        <v>2168</v>
       </c>
       <c r="C2" t="n">
-        <v>10242</v>
+        <v>4783</v>
       </c>
       <c r="D2" t="n">
-        <v>32506</v>
+        <v>28445</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4150</v>
+        <v>2716</v>
       </c>
       <c r="C3" t="n">
-        <v>5486</v>
+        <v>5015</v>
       </c>
       <c r="D3" t="n">
-        <v>5909</v>
+        <v>10352</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2799</v>
+        <v>1867</v>
       </c>
       <c r="C4" t="n">
-        <v>4158</v>
+        <v>4710</v>
       </c>
       <c r="D4" t="n">
-        <v>1991</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>742</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>1533</v>
+        <v>621</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5620</v>
+        <v>1829</v>
       </c>
       <c r="C2" t="n">
-        <v>10871</v>
+        <v>8999</v>
       </c>
       <c r="D2" t="n">
-        <v>26517</v>
+        <v>24352</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3727</v>
+        <v>2030</v>
       </c>
       <c r="C3" t="n">
-        <v>6876</v>
+        <v>4231</v>
       </c>
       <c r="D3" t="n">
-        <v>9535</v>
+        <v>12501</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2961</v>
+        <v>1976</v>
       </c>
       <c r="C4" t="n">
-        <v>4772</v>
+        <v>4784</v>
       </c>
       <c r="D4" t="n">
-        <v>2645</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1440</v>
+        <v>972</v>
       </c>
       <c r="C5" t="n">
-        <v>2821</v>
+        <v>2845</v>
       </c>
       <c r="D5" t="n">
-        <v>1291</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>249</v>
       </c>
       <c r="C6" t="n">
-        <v>914</v>
+        <v>448</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8771</v>
+        <v>1879</v>
       </c>
       <c r="C2" t="n">
-        <v>6502</v>
+        <v>7855</v>
       </c>
       <c r="D2" t="n">
-        <v>30088</v>
+        <v>18435</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3360</v>
+        <v>1607</v>
       </c>
       <c r="C3" t="n">
-        <v>7278</v>
+        <v>5818</v>
       </c>
       <c r="D3" t="n">
-        <v>10767</v>
+        <v>13422</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2056</v>
+        <v>1721</v>
       </c>
       <c r="C4" t="n">
-        <v>4836</v>
+        <v>4387</v>
       </c>
       <c r="D4" t="n">
-        <v>3336</v>
+        <v>5567</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1152</v>
+        <v>1269</v>
       </c>
       <c r="C5" t="n">
-        <v>2763</v>
+        <v>3791</v>
       </c>
       <c r="D5" t="n">
-        <v>1193</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>419</v>
+        <v>519</v>
       </c>
       <c r="C6" t="n">
-        <v>1250</v>
+        <v>1639</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7751</v>
+        <v>2245</v>
       </c>
       <c r="C2" t="n">
-        <v>5673</v>
+        <v>7301</v>
       </c>
       <c r="D2" t="n">
-        <v>22090</v>
+        <v>28036</v>
       </c>
     </row>
     <row r="3">
@@ -6081,10 +6081,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5022</v>
+        <v>1428</v>
       </c>
       <c r="C3" t="n">
-        <v>5880</v>
+        <v>5948</v>
       </c>
       <c r="D3" t="n">
         <v>13220</v>
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2364</v>
+        <v>1452</v>
       </c>
       <c r="C4" t="n">
-        <v>6188</v>
+        <v>4967</v>
       </c>
       <c r="D4" t="n">
-        <v>4732</v>
+        <v>6755</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1429</v>
+        <v>1307</v>
       </c>
       <c r="C5" t="n">
-        <v>3899</v>
+        <v>4003</v>
       </c>
       <c r="D5" t="n">
-        <v>1556</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>773</v>
       </c>
       <c r="C6" t="n">
-        <v>2077</v>
+        <v>2634</v>
       </c>
       <c r="D6" t="n">
-        <v>835</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>859</v>
+        <v>950</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6636</v>
+        <v>2027</v>
       </c>
       <c r="C2" t="n">
-        <v>5584</v>
+        <v>4555</v>
       </c>
       <c r="D2" t="n">
-        <v>17494</v>
+        <v>22009</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5201</v>
+        <v>2222</v>
       </c>
       <c r="C3" t="n">
-        <v>5014</v>
+        <v>8663</v>
       </c>
       <c r="D3" t="n">
-        <v>13637</v>
+        <v>14990</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3141</v>
+        <v>1207</v>
       </c>
       <c r="C4" t="n">
-        <v>5831</v>
+        <v>6942</v>
       </c>
       <c r="D4" t="n">
-        <v>6090</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1652</v>
+        <v>714</v>
       </c>
       <c r="C5" t="n">
-        <v>5048</v>
+        <v>2581</v>
       </c>
       <c r="D5" t="n">
-        <v>2088</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>2998</v>
+        <v>931</v>
       </c>
       <c r="D6" t="n">
-        <v>939</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>1479</v>
+        <v>322</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>578</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
